--- a/docs/Top Positions Data.XLSX
+++ b/docs/Top Positions Data.XLSX
@@ -1,34 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Portfolio\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF20E7A-36F3-4959-9606-49000BECADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89599E7B-CED5-4256-A96C-C33ACBBAD6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="12216" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Company</t>
   </si>
@@ -42,18 +53,12 @@
     <t>UNH</t>
   </si>
   <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
     <t>AMZN</t>
   </si>
   <si>
     <t>META</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
     <t>BBAI</t>
   </si>
   <si>
@@ -69,12 +74,6 @@
     <t>Amazon.com, Inc.</t>
   </si>
   <si>
-    <t>Alphabet Inc.</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V.</t>
-  </si>
-  <si>
     <t>Meta Platforms, Inc.</t>
   </si>
   <si>
@@ -91,12 +90,27 @@
   </si>
   <si>
     <t>UnitedHealth Group Inc.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>AI Hyperscaler</t>
+  </si>
+  <si>
+    <t>SaaS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,7 +142,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,110 +436,112 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>6.4000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.09</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.9E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
       <c r="C8" s="1">
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C10">
-      <sortCondition descending="1" ref="C1:C10"/>
+  <autoFilter ref="A1:C8" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C8">
+      <sortCondition descending="1" ref="C1:C8"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
